--- a/artfynd/A 61810-2024 artfynd.xlsx
+++ b/artfynd/A 61810-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130187682</v>
       </c>
       <c r="B2" t="n">
-        <v>80104</v>
+        <v>80189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130187681</v>
       </c>
       <c r="B3" t="n">
-        <v>80104</v>
+        <v>80189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 61810-2024 artfynd.xlsx
+++ b/artfynd/A 61810-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130187682</v>
       </c>
       <c r="B2" t="n">
-        <v>80189</v>
+        <v>80192</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130187681</v>
       </c>
       <c r="B3" t="n">
-        <v>80189</v>
+        <v>80192</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 61810-2024 artfynd.xlsx
+++ b/artfynd/A 61810-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130187682</v>
       </c>
       <c r="B2" t="n">
-        <v>80192</v>
+        <v>80218</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130187681</v>
       </c>
       <c r="B3" t="n">
-        <v>80192</v>
+        <v>80218</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 61810-2024 artfynd.xlsx
+++ b/artfynd/A 61810-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130187682</v>
       </c>
       <c r="B2" t="n">
-        <v>80218</v>
+        <v>80220</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130187681</v>
       </c>
       <c r="B3" t="n">
-        <v>80218</v>
+        <v>80220</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
